--- a/Excel/single.xlsx
+++ b/Excel/single.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\MHFramework\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDE41B1-BC61-4ED3-917A-E194526BF1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A1D441-E1BC-42AF-95BF-B4601A475C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="442">
   <si>
     <t>##var</t>
   </si>
@@ -30,6 +30,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -40,6 +41,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -67,6 +69,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -77,6 +80,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -215,6 +219,1197 @@
   </si>
   <si>
     <t>邮件炸弹</t>
+  </si>
+  <si>
+    <t>用于检查Windows系统中弱口令的安全软件工具是</t>
+  </si>
+  <si>
+    <t>L0phtCrack</t>
+  </si>
+  <si>
+    <t>SuperScan</t>
+  </si>
+  <si>
+    <t>COPS</t>
+  </si>
+  <si>
+    <t>Ethereal</t>
+  </si>
+  <si>
+    <t>利用电子邮件进行攻击的恶意代码是</t>
+  </si>
+  <si>
+    <t>Mydoom</t>
+  </si>
+  <si>
+    <t>netbul</t>
+  </si>
+  <si>
+    <t>Netspy</t>
+  </si>
+  <si>
+    <t>SubSeven</t>
+  </si>
+  <si>
+    <t>黑客拟获取远程主机的操作系统类型，可以选用的工具是</t>
+  </si>
+  <si>
+    <t>nmap</t>
+  </si>
+  <si>
+    <t>net</t>
+  </si>
+  <si>
+    <t>whisker</t>
+  </si>
+  <si>
+    <t>nbstat</t>
+  </si>
+  <si>
+    <t>一般来说，个人计算机的防病毒软件对（）是无效的</t>
+  </si>
+  <si>
+    <t>DDoS</t>
+  </si>
+  <si>
+    <t>Word病毒</t>
+  </si>
+  <si>
+    <t>木马</t>
+  </si>
+  <si>
+    <t>电子邮件病毒</t>
+  </si>
+  <si>
+    <t>Linux用户需要检查从网上下载到的文件是否被改动，可以用的安全工具是</t>
+  </si>
+  <si>
+    <t>md5sum</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>DES</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>专用于窃听网上传输的口令信息的工具是</t>
+  </si>
+  <si>
+    <t>dsniff</t>
+  </si>
+  <si>
+    <t>PGP</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>strobe</t>
+  </si>
+  <si>
+    <t>被喻为“瑞士军刀”的安全工具是</t>
+  </si>
+  <si>
+    <t>netcat</t>
+  </si>
+  <si>
+    <t>WUPS</t>
+  </si>
+  <si>
+    <t>NetScanTools</t>
+  </si>
+  <si>
+    <t>用于提取Windows2000系统中用户账号信息的工具是</t>
+  </si>
+  <si>
+    <t>pwdump2</t>
+  </si>
+  <si>
+    <t>tcpdump</t>
+  </si>
+  <si>
+    <t>Winzapper</t>
+  </si>
+  <si>
+    <t>dump</t>
+  </si>
+  <si>
+    <t>Windows系统中容纳SID的数量是</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>“冲击波”蠕虫利用Windows系统漏洞是</t>
+  </si>
+  <si>
+    <t>RPC漏洞</t>
+  </si>
+  <si>
+    <t>SQL中sa空口令漏洞</t>
+  </si>
+  <si>
+    <t>WebDav漏洞</t>
+  </si>
+  <si>
+    <t>、ida漏洞</t>
+  </si>
+  <si>
+    <t>黑客在受害主机上安装（），可以防止系统管理员用ps或netstat发现</t>
+  </si>
+  <si>
+    <t>rootkit</t>
+  </si>
+  <si>
+    <t>adore</t>
+  </si>
+  <si>
+    <t>fpipe</t>
+  </si>
+  <si>
+    <t>NetBus</t>
+  </si>
+  <si>
+    <t>用于获取防火墙配置信息的安全工具是</t>
+  </si>
+  <si>
+    <t>hping</t>
+  </si>
+  <si>
+    <t>Loki</t>
+  </si>
+  <si>
+    <t>Flawfinder</t>
+  </si>
+  <si>
+    <t>firewalk</t>
+  </si>
+  <si>
+    <t>在Windows2000/XP中，取消IPCS默认共享的操作是</t>
+  </si>
+  <si>
+    <t>netshareIPCS/delete</t>
+  </si>
+  <si>
+    <t>netshare/delIPCS</t>
+  </si>
+  <si>
+    <t>netshare/deleteIPCS</t>
+  </si>
+  <si>
+    <t>netIPCS/delete</t>
+  </si>
+  <si>
+    <t>在Linux系统中，显示内核模块的命令是</t>
+  </si>
+  <si>
+    <t>Ismod</t>
+  </si>
+  <si>
+    <t>ls</t>
+  </si>
+  <si>
+    <t>LKM</t>
+  </si>
+  <si>
+    <t>mod</t>
+  </si>
+  <si>
+    <t>Windows系统中域控制器能够容纳SID的数量是</t>
+  </si>
+  <si>
+    <t>40亿</t>
+  </si>
+  <si>
+    <t>99亿</t>
+  </si>
+  <si>
+    <t>50亿</t>
+  </si>
+  <si>
+    <t>60亿</t>
+  </si>
+  <si>
+    <t>计算机技术和通信技术紧密相结合的产物是</t>
+  </si>
+  <si>
+    <t>计算机网络</t>
+  </si>
+  <si>
+    <t>计算机系统</t>
+  </si>
+  <si>
+    <t>信息录入系统</t>
+  </si>
+  <si>
+    <t>信息管理系统</t>
+  </si>
+  <si>
+    <t>网络资源管理中的资源指_</t>
+  </si>
+  <si>
+    <t>计算机资源</t>
+  </si>
+  <si>
+    <t>硬件资源</t>
+  </si>
+  <si>
+    <t>通信资源</t>
+  </si>
+  <si>
+    <t>A和C</t>
+  </si>
+  <si>
+    <t>通过为系统的关键部件设置余备份、并在发生故障时通过自动功能隔离和自动功能转移使系统不间断地工作的计算机是</t>
+  </si>
+  <si>
+    <t>容错计算机</t>
+  </si>
+  <si>
+    <t>个人计算机</t>
+  </si>
+  <si>
+    <t>图形工作站</t>
+  </si>
+  <si>
+    <t>家用计算机</t>
+  </si>
+  <si>
+    <t>构建网络安全的第一防线是</t>
+  </si>
+  <si>
+    <t>法律</t>
+  </si>
+  <si>
+    <t>安全技术</t>
+  </si>
+  <si>
+    <t>防范计算机病毒</t>
+  </si>
+  <si>
+    <t>网络结构</t>
+  </si>
+  <si>
+    <t>《中华人民共和国计算机计算机信息系统安全保护条例》规定，国家对计算机信息系统安全专用产品的销售实行</t>
+  </si>
+  <si>
+    <t>许可证制度</t>
+  </si>
+  <si>
+    <t>3C认证</t>
+  </si>
+  <si>
+    <t>ISO9000</t>
+  </si>
+  <si>
+    <t>专买制度</t>
+  </si>
+  <si>
+    <t>通过信息系统自动记录下网络中机器的使用时间、敏感操作和违纪操作等对计算机网络系统加以保护的技术被称为</t>
+  </si>
+  <si>
+    <t>审计技术</t>
+  </si>
+  <si>
+    <t>反计算机病毒技术</t>
+  </si>
+  <si>
+    <t>入侵检测技术</t>
+  </si>
+  <si>
+    <t>防火墙技术</t>
+  </si>
+  <si>
+    <t>用倒影射单字母加密方法对单词computer加密后的结果为</t>
+  </si>
+  <si>
+    <t>xlnkfgvi</t>
+  </si>
+  <si>
+    <t>xlnkfjui</t>
+  </si>
+  <si>
+    <t>xlnkfjvi</t>
+  </si>
+  <si>
+    <t>xlnkfhvi</t>
+  </si>
+  <si>
+    <t>防止静态信息被非授权访问和防止动态信息被截取解密是</t>
+  </si>
+  <si>
+    <t>数据保密性</t>
+  </si>
+  <si>
+    <t>数据完整性</t>
+  </si>
+  <si>
+    <t>数据可用性</t>
+  </si>
+  <si>
+    <t>数据可靠性</t>
+  </si>
+  <si>
+    <t>限制被保护网络与因特网之间或其他网络之间信息访问的部件或部件集被称</t>
+  </si>
+  <si>
+    <t>防火墙系统</t>
+  </si>
+  <si>
+    <t>入侵检测系统</t>
+  </si>
+  <si>
+    <t>加密系统</t>
+  </si>
+  <si>
+    <t>认证系统</t>
+  </si>
+  <si>
+    <t>总线型结构是从网络服务器中引出一条电缆，网络中所有的工作站依次连接到这条电缆上的各个节点的体系结构。这种网络结构也称为</t>
+  </si>
+  <si>
+    <t>多点结构</t>
+  </si>
+  <si>
+    <t>星型结构</t>
+  </si>
+  <si>
+    <t>网状结构</t>
+  </si>
+  <si>
+    <t>树型结构</t>
+  </si>
+  <si>
+    <t>用来把主机连接在一起并在主机之间传送信息的设施，被称为</t>
+  </si>
+  <si>
+    <t>通信子网</t>
+  </si>
+  <si>
+    <t>路由器</t>
+  </si>
+  <si>
+    <t>资源子网</t>
+  </si>
+  <si>
+    <t>主机</t>
+  </si>
+  <si>
+    <t>计算机网络系统中硬件结构中不包括</t>
+  </si>
+  <si>
+    <t>系统软件</t>
+  </si>
+  <si>
+    <t>网络接口</t>
+  </si>
+  <si>
+    <t>传输介质</t>
+  </si>
+  <si>
+    <t>计算机主机</t>
+  </si>
+  <si>
+    <t>下面哪些不是SAN的主要构成组件</t>
+  </si>
+  <si>
+    <t>CISCO路由器</t>
+  </si>
+  <si>
+    <t>HBA卡</t>
+  </si>
+  <si>
+    <t>GBIC（光电转换模块）</t>
+  </si>
+  <si>
+    <t>光纤交换机</t>
+  </si>
+  <si>
+    <t>现今病毒、蠕虫的复制传播特点使得攻击程序如虎添翼，这体现了网络攻击的（）发展趋势</t>
+  </si>
+  <si>
+    <t>网络攻击的协同化</t>
+  </si>
+  <si>
+    <t>网络攻击人群的大众化</t>
+  </si>
+  <si>
+    <t>网络攻击的野蛮化</t>
+  </si>
+  <si>
+    <t>网络攻击的智能化</t>
+  </si>
+  <si>
+    <t>在大家熟知的病毒蠕虫之中，下列哪项不具备通过网络复制传播的特性</t>
+  </si>
+  <si>
+    <t>CIH</t>
+  </si>
+  <si>
+    <t>红色代码</t>
+  </si>
+  <si>
+    <t>尼姆达(Nimda）</t>
+  </si>
+  <si>
+    <t>狮子王(SQLSlammer）</t>
+  </si>
+  <si>
+    <t>网络监听(嗅探、的这种攻击形式破坏了下列哪项内容</t>
+  </si>
+  <si>
+    <t>网络信息的保密性</t>
+  </si>
+  <si>
+    <t>网络服务的可用性</t>
+  </si>
+  <si>
+    <t>网络信息的完整性</t>
+  </si>
+  <si>
+    <t>网络信息的抗抵赖性</t>
+  </si>
+  <si>
+    <t>会话劫持的这种攻击形式破坏了下列哪项内容</t>
+  </si>
+  <si>
+    <t>拒绝服务攻击的这种攻击形式破坏了下列哪项内容</t>
+  </si>
+  <si>
+    <t>在网络攻击模型中下列哪种攻击过程不属于预攻击阶段</t>
+  </si>
+  <si>
+    <t>身份隐藏</t>
+  </si>
+  <si>
+    <t>开辟后门</t>
+  </si>
+  <si>
+    <t>弱点挖掘</t>
+  </si>
+  <si>
+    <t>信息收集</t>
+  </si>
+  <si>
+    <t>在下列这些网络攻击模型的攻击过程中，端口扫描攻击一般属于</t>
+  </si>
+  <si>
+    <t>攻击实施</t>
+  </si>
+  <si>
+    <t>痕迹清除</t>
+  </si>
+  <si>
+    <t>在进行网络攻击身份隐藏的时候，下列哪~项网络信息不能被欺骗或盗用?</t>
+  </si>
+  <si>
+    <t>以上都不是</t>
+  </si>
+  <si>
+    <t>MAC地址</t>
+  </si>
+  <si>
+    <t>IP地址</t>
+  </si>
+  <si>
+    <t>邮件账户</t>
+  </si>
+  <si>
+    <t>SSH（SecureShell）协议及某软件工具用来对下列哪种数据进行加密?</t>
+  </si>
+  <si>
+    <t>电子邮件</t>
+  </si>
+  <si>
+    <t>网络通信</t>
+  </si>
+  <si>
+    <t>语音电话</t>
+  </si>
+  <si>
+    <t>硬盘数据</t>
+  </si>
+  <si>
+    <t>下列哪种网络通信协议对传输的数据会进行加密来保证信息的保密性</t>
+  </si>
+  <si>
+    <t>SSL</t>
+  </si>
+  <si>
+    <t>FTP</t>
+  </si>
+  <si>
+    <t>POP3</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>调试分析漏洞的工具是</t>
+  </si>
+  <si>
+    <t>Ollydbg</t>
+  </si>
+  <si>
+    <t>IDAPro</t>
+  </si>
+  <si>
+    <t>GHOST</t>
+  </si>
+  <si>
+    <t>gdb</t>
+  </si>
+  <si>
+    <t>《计算机病毒防治管理办法》规定，（）公共信息网络监察部门主管全国的计算机病毒防治管理工作</t>
+  </si>
+  <si>
+    <t>公安部</t>
+  </si>
+  <si>
+    <t>安全部</t>
+  </si>
+  <si>
+    <t>信息产业部</t>
+  </si>
+  <si>
+    <t>国家保密委员会</t>
+  </si>
+  <si>
+    <t>拒绝服务攻击的后果是</t>
+  </si>
+  <si>
+    <t>上面几项都是</t>
+  </si>
+  <si>
+    <t>信息不可用</t>
+  </si>
+  <si>
+    <t>应用程序不可用</t>
+  </si>
+  <si>
+    <t>阻止通信</t>
+  </si>
+  <si>
+    <t>下面不属于PKI组成部分的是</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>证书主体</t>
+  </si>
+  <si>
+    <t>用证书的应用和系统</t>
+  </si>
+  <si>
+    <t>书权威机构</t>
+  </si>
+  <si>
+    <t>信息安全经历了三个发展阶段，以下（）不是这三个发展阶段</t>
+  </si>
+  <si>
+    <t>安全保障阶段</t>
+  </si>
+  <si>
+    <t>信息安全阶段</t>
+  </si>
+  <si>
+    <t>通信保密阶段</t>
+  </si>
+  <si>
+    <t>加密机阶段</t>
+  </si>
+  <si>
+    <t>下列（）不属于信息安全阶段的三个基本属性</t>
+  </si>
+  <si>
+    <t>不可否认性</t>
+  </si>
+  <si>
+    <t>保密性</t>
+  </si>
+  <si>
+    <t>完整性</t>
+  </si>
+  <si>
+    <t>可用性</t>
+  </si>
+  <si>
+    <t>计算机网络是地理上分散的多台（）遵循约定的通信协议，通过软硬件互联的系统</t>
+  </si>
+  <si>
+    <t>自主计算机</t>
+  </si>
+  <si>
+    <t>计算机</t>
+  </si>
+  <si>
+    <t>主从计算机</t>
+  </si>
+  <si>
+    <t>数字设备</t>
+  </si>
+  <si>
+    <t>网络安全是分布网络环境中对（）提供安全保护</t>
+  </si>
+  <si>
+    <t>上面3项都是</t>
+  </si>
+  <si>
+    <t>信息载体</t>
+  </si>
+  <si>
+    <t>信息的处理、传输</t>
+  </si>
+  <si>
+    <t>信息的存储、访问</t>
+  </si>
+  <si>
+    <t>网络安全的基本属性是（）</t>
+  </si>
+  <si>
+    <t>机密性</t>
+  </si>
+  <si>
+    <t>密码学的目的是（）</t>
+  </si>
+  <si>
+    <t>研究数据保密</t>
+  </si>
+  <si>
+    <t>研究信息安全</t>
+  </si>
+  <si>
+    <t>研究数据加密</t>
+  </si>
+  <si>
+    <t>研究数据解密</t>
+  </si>
+  <si>
+    <t>可信计算机系统评估准则（TrustedComputerSystemEvaluationCriteria，TCSEC）共分为（）大类（）级</t>
+  </si>
+  <si>
+    <t>4、7</t>
+  </si>
+  <si>
+    <t>3、7</t>
+  </si>
+  <si>
+    <t>4、5</t>
+  </si>
+  <si>
+    <t>4、6</t>
+  </si>
+  <si>
+    <t>以下操作系统中属于D级安全的是</t>
+  </si>
+  <si>
+    <t>运行非UNIX的Macintosh机</t>
+  </si>
+  <si>
+    <t>运行Linux的PC</t>
+  </si>
+  <si>
+    <t>UNIX系统</t>
+  </si>
+  <si>
+    <t>XENIX</t>
+  </si>
+  <si>
+    <t>计算机病毒是计算机系统中一类隐藏在（）上蓄意破坏的捣乱程序</t>
+  </si>
+  <si>
+    <t>存储介质</t>
+  </si>
+  <si>
+    <t>网络</t>
+  </si>
+  <si>
+    <t>内存</t>
+  </si>
+  <si>
+    <t>软盘</t>
+  </si>
+  <si>
+    <t>对攻击可能性的分析在很大程度上带有（）</t>
+  </si>
+  <si>
+    <t>主观性</t>
+  </si>
+  <si>
+    <t>盲目性</t>
+  </si>
+  <si>
+    <t>上面3项都不是</t>
+  </si>
+  <si>
+    <t>客观性</t>
+  </si>
+  <si>
+    <t>从安全属性对各种网络攻击进行分类，阻断攻击是针对（）的攻击</t>
+  </si>
+  <si>
+    <t>真实性</t>
+  </si>
+  <si>
+    <t>从安全属性对各种网络攻击进行分类，截获攻击是针对（）的攻击</t>
+  </si>
+  <si>
+    <t>威胁是一个可能破坏信息系统环境安全的动作或事件，威胁包括（）。</t>
+  </si>
+  <si>
+    <t>以上三项都是</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>代理</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>对目标的攻击威胁通常通过代理实现，而代理需要的特性包括（）</t>
+  </si>
+  <si>
+    <t>上面三项都是</t>
+  </si>
+  <si>
+    <t>对目标发出威胁的动机</t>
+  </si>
+  <si>
+    <t>有关目标的知识</t>
+  </si>
+  <si>
+    <t>访问目标能力</t>
+  </si>
+  <si>
+    <t>拒绝服务攻击的后果是（）</t>
+  </si>
+  <si>
+    <t>系统宕机</t>
+  </si>
+  <si>
+    <t>机密性服务提供信息的保密，机密性服务包括（）。</t>
+  </si>
+  <si>
+    <t>通信流的机密性</t>
+  </si>
+  <si>
+    <t>信息传输机密性</t>
+  </si>
+  <si>
+    <t>文件的机密性</t>
+  </si>
+  <si>
+    <t>完整性服务提供信息的正确性。该服务必须和（）服务配合工作，才能对抗篡改攻击</t>
+  </si>
+  <si>
+    <t>可审性</t>
+  </si>
+  <si>
+    <t>下列对访问控制影响不大的是（）</t>
+  </si>
+  <si>
+    <t>主体与客体的类型</t>
+  </si>
+  <si>
+    <t>访问类型</t>
+  </si>
+  <si>
+    <t>客体身份</t>
+  </si>
+  <si>
+    <t>主体身份</t>
+  </si>
+  <si>
+    <t>下面（）的存储提供最高安全</t>
+  </si>
+  <si>
+    <t>硬件分段</t>
+  </si>
+  <si>
+    <t>虚拟机</t>
+  </si>
+  <si>
+    <t>保护环</t>
+  </si>
+  <si>
+    <t>内存映射</t>
+  </si>
+  <si>
+    <t>一种抽象机能保证所有的主体有适当的允许权来访问客体，这种确保客体不被不可信的主体损害的安全控制概念是（）</t>
+  </si>
+  <si>
+    <t>基准监控器</t>
+  </si>
+  <si>
+    <t>安全域</t>
+  </si>
+  <si>
+    <t>TCB</t>
+  </si>
+  <si>
+    <t>安全核</t>
+  </si>
+  <si>
+    <t>TCB内有几种的类型部件，下列（）不在安全边界内</t>
+  </si>
+  <si>
+    <t>应用程序</t>
+  </si>
+  <si>
+    <t>保护的硬件组件</t>
+  </si>
+  <si>
+    <t>基准监控器和安全核</t>
+  </si>
+  <si>
+    <t>母板上的固件</t>
+  </si>
+  <si>
+    <t>处理器和系统运行在（）状态能处理和硬件的直接通信</t>
+  </si>
+  <si>
+    <t>特权状态</t>
+  </si>
+  <si>
+    <t>运行状态</t>
+  </si>
+  <si>
+    <t>等待状态</t>
+  </si>
+  <si>
+    <t>问题状态</t>
+  </si>
+  <si>
+    <t>ISO7498-2从体系结构的观点描述了5种可选的安全服务，以下不属于这5种安全服务的是（）。</t>
+  </si>
+  <si>
+    <t>数据报过滤</t>
+  </si>
+  <si>
+    <t>身份鉴别</t>
+  </si>
+  <si>
+    <t>授权控制</t>
+  </si>
+  <si>
+    <t>ISO7498-2描述了8种特定的安全机制，以下不属于这8种安全机制的是（）。</t>
+  </si>
+  <si>
+    <t>安全标记机制</t>
+  </si>
+  <si>
+    <t>加密机制</t>
+  </si>
+  <si>
+    <t>数字签名机制</t>
+  </si>
+  <si>
+    <t>访问控制机制</t>
+  </si>
+  <si>
+    <t>ISO7498-2从体系结构的观点描述了5种普遍性的安全机制，这5种安全机制不包括</t>
+  </si>
+  <si>
+    <t>数据完整性机制</t>
+  </si>
+  <si>
+    <t>可信功能</t>
+  </si>
+  <si>
+    <t>安全标号</t>
+  </si>
+  <si>
+    <t>事件检测</t>
+  </si>
+  <si>
+    <t>在ISO/OSI定义的安全体系结构中，没有规定（）</t>
+  </si>
+  <si>
+    <t>数据可用性安全服务</t>
+  </si>
+  <si>
+    <t>访问控制安全服务</t>
+  </si>
+  <si>
+    <t>对象认证服务</t>
+  </si>
+  <si>
+    <t>数据保密性安全服务</t>
+  </si>
+  <si>
+    <t>（）不属于ISO/OSI安全体系结构的安全机制</t>
+  </si>
+  <si>
+    <t>审计机制</t>
+  </si>
+  <si>
+    <t>公正机制</t>
+  </si>
+  <si>
+    <t>分组过滤型防火墙原理上是基于（）进行分析的技术</t>
+  </si>
+  <si>
+    <t>网络层</t>
+  </si>
+  <si>
+    <t>数据链路层</t>
+  </si>
+  <si>
+    <t>应用层</t>
+  </si>
+  <si>
+    <t>物理层</t>
+  </si>
+  <si>
+    <t>ISO/IEC网络安全体系结构的安全维包含（）个安全度量，用于实施网络安全的某一特定方面的安全控制措施</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>通常所说的移动VPN是指（）</t>
+  </si>
+  <si>
+    <t>AccessVPN</t>
+  </si>
+  <si>
+    <t>IntranetVPN</t>
+  </si>
+  <si>
+    <t>ExtranetVPN</t>
+  </si>
+  <si>
+    <t>以上皆不是</t>
+  </si>
+  <si>
+    <t>属于第二层的VPN隧道协议有（）</t>
+  </si>
+  <si>
+    <t>PPTP</t>
+  </si>
+  <si>
+    <t>IPSec</t>
+  </si>
+  <si>
+    <t>GRE</t>
+  </si>
+  <si>
+    <t>GRE协议（）</t>
+  </si>
+  <si>
+    <t>只封装，不加密</t>
+  </si>
+  <si>
+    <t>既封装，又加密</t>
+  </si>
+  <si>
+    <t>不封装，只加密</t>
+  </si>
+  <si>
+    <t>不封装，不加密</t>
+  </si>
+  <si>
+    <t>PPTP客户端使用（）建立连接</t>
+  </si>
+  <si>
+    <t>CP协议</t>
+  </si>
+  <si>
+    <t>UDP协议</t>
+  </si>
+  <si>
+    <t>L2TP协议</t>
+  </si>
+  <si>
+    <t>GRE协议的乘客协议是（）</t>
+  </si>
+  <si>
+    <t>以上皆可</t>
+  </si>
+  <si>
+    <t>IPX</t>
+  </si>
+  <si>
+    <t>AppleTalk</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>IPSec协议和（）VPN隧道协议处于同一层。</t>
+  </si>
+  <si>
+    <t>以上皆是</t>
+  </si>
+  <si>
+    <t>L2TP</t>
+  </si>
+  <si>
+    <t>ESP协议中不是必须实现的验证算法的是（）</t>
+  </si>
+  <si>
+    <t>HMAC-RIPEMD-160</t>
+  </si>
+  <si>
+    <t>HMAC-SHA1</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>HMACMD5</t>
+  </si>
+  <si>
+    <t>（）协议必须提供验证服务</t>
+  </si>
+  <si>
+    <t>AH</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>下列协议中，（）协议的数据可以收到IPSec的保护</t>
+  </si>
+  <si>
+    <t>TCP、UDP、IP</t>
+  </si>
+  <si>
+    <t>RCP</t>
+  </si>
+  <si>
+    <t>RARP</t>
+  </si>
+  <si>
+    <t>“会话侦听与劫持技术”属于（）技术</t>
+  </si>
+  <si>
+    <t>协议漏洞渗透</t>
+  </si>
+  <si>
+    <t>密码分析还原</t>
+  </si>
+  <si>
+    <t>应用漏洞分析与渗透</t>
+  </si>
+  <si>
+    <t>DoS攻击</t>
+  </si>
+  <si>
+    <t>KMI/PKI支持的服务不包括（）</t>
+  </si>
+  <si>
+    <t>访问控制服务</t>
+  </si>
+  <si>
+    <t>目录服务</t>
+  </si>
+  <si>
+    <t>对称密钥的产生和吩咐</t>
+  </si>
+  <si>
+    <t>非对称密钥技术及证书管理</t>
+  </si>
+  <si>
+    <t>有意避开系统访问控制机制，对网络设备及资源进行非正常使用属于</t>
+  </si>
+  <si>
+    <t>非授权访问</t>
+  </si>
+  <si>
+    <t>破环数据完整性</t>
+  </si>
+  <si>
+    <t>信息泄漏</t>
+  </si>
+  <si>
+    <t>拒绝服务攻击</t>
+  </si>
+  <si>
+    <t>利用以太网的特点，将设备网卡设置为“混杂模式”，从而能够接受到整个以太网内的网络数据信息</t>
+  </si>
+  <si>
+    <t>嗅探程序</t>
+  </si>
+  <si>
+    <t>木马程序</t>
+  </si>
+  <si>
+    <t>缓冲区溢出攻击</t>
+  </si>
+  <si>
+    <t>字典攻击被用于</t>
+  </si>
+  <si>
+    <t>破解密码</t>
+  </si>
+  <si>
+    <t>远程登录</t>
+  </si>
+  <si>
+    <t>用户欺骗</t>
+  </si>
+  <si>
+    <t>网络嗅探</t>
+  </si>
+  <si>
+    <t>ARP属于()协议</t>
+  </si>
+  <si>
+    <t>传输层</t>
+  </si>
+  <si>
+    <t>在下面4种病毒中，(C)可以远程控制网络中的计算机</t>
+  </si>
+  <si>
+    <t>Trojan.qq3344</t>
+  </si>
+  <si>
+    <t>Macro.Melissa</t>
+  </si>
+  <si>
+    <t>Win32.CIH</t>
+  </si>
+  <si>
+    <t>worm.Sasser.f</t>
+  </si>
+  <si>
+    <t>ARP木马利用（）协议设计之初没有任何验证功能这一漏洞而实施破坏</t>
+  </si>
+  <si>
+    <t>ARP</t>
+  </si>
+  <si>
+    <t>以上都是</t>
+  </si>
+  <si>
+    <t>ICMP</t>
   </si>
 </sst>
 </file>
@@ -233,6 +1428,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -240,12 +1436,14 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -615,7 +1813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -954,6 +2152,2030 @@
         <v>44</v>
       </c>
     </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" t="s">
+        <v>132</v>
+      </c>
+      <c r="H28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" t="s">
+        <v>150</v>
+      </c>
+      <c r="E32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G32" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" t="s">
+        <v>162</v>
+      </c>
+      <c r="H34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35" t="s">
+        <v>166</v>
+      </c>
+      <c r="G35" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" t="s">
+        <v>171</v>
+      </c>
+      <c r="G36" t="s">
+        <v>172</v>
+      </c>
+      <c r="H36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
+        <v>175</v>
+      </c>
+      <c r="F37" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" t="s">
+        <v>181</v>
+      </c>
+      <c r="G38" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" t="s">
+        <v>187</v>
+      </c>
+      <c r="H39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" t="s">
+        <v>190</v>
+      </c>
+      <c r="F40" t="s">
+        <v>191</v>
+      </c>
+      <c r="G40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" t="s">
+        <v>195</v>
+      </c>
+      <c r="F41" t="s">
+        <v>196</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" t="s">
+        <v>195</v>
+      </c>
+      <c r="F42" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" t="s">
+        <v>198</v>
+      </c>
+      <c r="F43" t="s">
+        <v>196</v>
+      </c>
+      <c r="G43" t="s">
+        <v>197</v>
+      </c>
+      <c r="H43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" t="s">
+        <v>202</v>
+      </c>
+      <c r="F44" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>40</v>
+      </c>
+      <c r="C45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D45" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" t="s">
+        <v>205</v>
+      </c>
+      <c r="F45" t="s">
+        <v>204</v>
+      </c>
+      <c r="G45" t="s">
+        <v>207</v>
+      </c>
+      <c r="H45" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" t="s">
+        <v>210</v>
+      </c>
+      <c r="E46" t="s">
+        <v>210</v>
+      </c>
+      <c r="F46" t="s">
+        <v>211</v>
+      </c>
+      <c r="G46" t="s">
+        <v>212</v>
+      </c>
+      <c r="H46" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>215</v>
+      </c>
+      <c r="F47" t="s">
+        <v>216</v>
+      </c>
+      <c r="G47" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" t="s">
+        <v>220</v>
+      </c>
+      <c r="E48" t="s">
+        <v>220</v>
+      </c>
+      <c r="F48" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48" t="s">
+        <v>222</v>
+      </c>
+      <c r="H48" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>224</v>
+      </c>
+      <c r="D49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E49" t="s">
+        <v>225</v>
+      </c>
+      <c r="F49" t="s">
+        <v>226</v>
+      </c>
+      <c r="G49" t="s">
+        <v>227</v>
+      </c>
+      <c r="H49" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>45</v>
+      </c>
+      <c r="C50" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" t="s">
+        <v>230</v>
+      </c>
+      <c r="E50" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" t="s">
+        <v>231</v>
+      </c>
+      <c r="G50" t="s">
+        <v>232</v>
+      </c>
+      <c r="H50" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>234</v>
+      </c>
+      <c r="D51" t="s">
+        <v>235</v>
+      </c>
+      <c r="E51" t="s">
+        <v>235</v>
+      </c>
+      <c r="F51" t="s">
+        <v>236</v>
+      </c>
+      <c r="G51" t="s">
+        <v>237</v>
+      </c>
+      <c r="H51" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>47</v>
+      </c>
+      <c r="C52" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" t="s">
+        <v>240</v>
+      </c>
+      <c r="E52" t="s">
+        <v>240</v>
+      </c>
+      <c r="F52" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" t="s">
+        <v>242</v>
+      </c>
+      <c r="H52" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>48</v>
+      </c>
+      <c r="C53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D53" t="s">
+        <v>245</v>
+      </c>
+      <c r="E53" t="s">
+        <v>245</v>
+      </c>
+      <c r="F53" t="s">
+        <v>246</v>
+      </c>
+      <c r="G53" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>49</v>
+      </c>
+      <c r="C54" t="s">
+        <v>249</v>
+      </c>
+      <c r="D54" t="s">
+        <v>250</v>
+      </c>
+      <c r="E54" t="s">
+        <v>250</v>
+      </c>
+      <c r="F54" t="s">
+        <v>251</v>
+      </c>
+      <c r="G54" t="s">
+        <v>252</v>
+      </c>
+      <c r="H54" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>50</v>
+      </c>
+      <c r="C55" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" t="s">
+        <v>255</v>
+      </c>
+      <c r="E55" t="s">
+        <v>255</v>
+      </c>
+      <c r="F55" t="s">
+        <v>256</v>
+      </c>
+      <c r="G55" t="s">
+        <v>257</v>
+      </c>
+      <c r="H55" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>51</v>
+      </c>
+      <c r="C56" t="s">
+        <v>259</v>
+      </c>
+      <c r="D56" t="s">
+        <v>260</v>
+      </c>
+      <c r="E56" t="s">
+        <v>260</v>
+      </c>
+      <c r="F56" t="s">
+        <v>261</v>
+      </c>
+      <c r="G56" t="s">
+        <v>262</v>
+      </c>
+      <c r="H56" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>52</v>
+      </c>
+      <c r="C57" t="s">
+        <v>264</v>
+      </c>
+      <c r="D57" t="s">
+        <v>260</v>
+      </c>
+      <c r="E57" t="s">
+        <v>260</v>
+      </c>
+      <c r="F57" t="s">
+        <v>265</v>
+      </c>
+      <c r="G57" t="s">
+        <v>253</v>
+      </c>
+      <c r="H57" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58">
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>266</v>
+      </c>
+      <c r="D58" t="s">
+        <v>267</v>
+      </c>
+      <c r="E58" t="s">
+        <v>267</v>
+      </c>
+      <c r="F58" t="s">
+        <v>268</v>
+      </c>
+      <c r="G58" t="s">
+        <v>269</v>
+      </c>
+      <c r="H58" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>54</v>
+      </c>
+      <c r="C59" t="s">
+        <v>271</v>
+      </c>
+      <c r="D59" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" t="s">
+        <v>272</v>
+      </c>
+      <c r="F59" t="s">
+        <v>273</v>
+      </c>
+      <c r="G59" t="s">
+        <v>274</v>
+      </c>
+      <c r="H59" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <v>55</v>
+      </c>
+      <c r="C60" t="s">
+        <v>276</v>
+      </c>
+      <c r="D60" t="s">
+        <v>277</v>
+      </c>
+      <c r="E60" t="s">
+        <v>277</v>
+      </c>
+      <c r="F60" t="s">
+        <v>278</v>
+      </c>
+      <c r="G60" t="s">
+        <v>279</v>
+      </c>
+      <c r="H60" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61">
+        <v>56</v>
+      </c>
+      <c r="C61" t="s">
+        <v>281</v>
+      </c>
+      <c r="D61" t="s">
+        <v>282</v>
+      </c>
+      <c r="E61" t="s">
+        <v>282</v>
+      </c>
+      <c r="F61" t="s">
+        <v>283</v>
+      </c>
+      <c r="G61" t="s">
+        <v>284</v>
+      </c>
+      <c r="H61" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62">
+        <v>57</v>
+      </c>
+      <c r="C62" t="s">
+        <v>286</v>
+      </c>
+      <c r="D62" t="s">
+        <v>287</v>
+      </c>
+      <c r="E62" t="s">
+        <v>287</v>
+      </c>
+      <c r="F62" t="s">
+        <v>288</v>
+      </c>
+      <c r="G62" t="s">
+        <v>289</v>
+      </c>
+      <c r="H62" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
+        <v>291</v>
+      </c>
+      <c r="D63" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" t="s">
+        <v>253</v>
+      </c>
+      <c r="F63" t="s">
+        <v>252</v>
+      </c>
+      <c r="G63" t="s">
+        <v>292</v>
+      </c>
+      <c r="H63" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>59</v>
+      </c>
+      <c r="C64" t="s">
+        <v>293</v>
+      </c>
+      <c r="D64" t="s">
+        <v>265</v>
+      </c>
+      <c r="E64" t="s">
+        <v>265</v>
+      </c>
+      <c r="F64" t="s">
+        <v>253</v>
+      </c>
+      <c r="G64" t="s">
+        <v>252</v>
+      </c>
+      <c r="H64" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>60</v>
+      </c>
+      <c r="C65" t="s">
+        <v>294</v>
+      </c>
+      <c r="D65" t="s">
+        <v>295</v>
+      </c>
+      <c r="E65" t="s">
+        <v>295</v>
+      </c>
+      <c r="F65" t="s">
+        <v>296</v>
+      </c>
+      <c r="G65" t="s">
+        <v>297</v>
+      </c>
+      <c r="H65" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <v>61</v>
+      </c>
+      <c r="C66" t="s">
+        <v>299</v>
+      </c>
+      <c r="D66" t="s">
+        <v>300</v>
+      </c>
+      <c r="E66" t="s">
+        <v>300</v>
+      </c>
+      <c r="F66" t="s">
+        <v>301</v>
+      </c>
+      <c r="G66" t="s">
+        <v>302</v>
+      </c>
+      <c r="H66" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67">
+        <v>62</v>
+      </c>
+      <c r="C67" t="s">
+        <v>304</v>
+      </c>
+      <c r="D67" t="s">
+        <v>235</v>
+      </c>
+      <c r="E67" t="s">
+        <v>235</v>
+      </c>
+      <c r="F67" t="s">
+        <v>236</v>
+      </c>
+      <c r="G67" t="s">
+        <v>305</v>
+      </c>
+      <c r="H67" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
+        <v>306</v>
+      </c>
+      <c r="D68" t="s">
+        <v>295</v>
+      </c>
+      <c r="E68" t="s">
+        <v>295</v>
+      </c>
+      <c r="F68" t="s">
+        <v>307</v>
+      </c>
+      <c r="G68" t="s">
+        <v>308</v>
+      </c>
+      <c r="H68" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <v>64</v>
+      </c>
+      <c r="C69" t="s">
+        <v>310</v>
+      </c>
+      <c r="D69" t="s">
+        <v>311</v>
+      </c>
+      <c r="E69" t="s">
+        <v>311</v>
+      </c>
+      <c r="F69" t="s">
+        <v>253</v>
+      </c>
+      <c r="G69" t="s">
+        <v>295</v>
+      </c>
+      <c r="H69" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70">
+        <v>65</v>
+      </c>
+      <c r="C70" t="s">
+        <v>312</v>
+      </c>
+      <c r="D70" t="s">
+        <v>313</v>
+      </c>
+      <c r="E70" t="s">
+        <v>313</v>
+      </c>
+      <c r="F70" t="s">
+        <v>314</v>
+      </c>
+      <c r="G70" t="s">
+        <v>315</v>
+      </c>
+      <c r="H70" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71">
+        <v>66</v>
+      </c>
+      <c r="C71" t="s">
+        <v>317</v>
+      </c>
+      <c r="D71" t="s">
+        <v>318</v>
+      </c>
+      <c r="E71" t="s">
+        <v>318</v>
+      </c>
+      <c r="F71" t="s">
+        <v>319</v>
+      </c>
+      <c r="G71" t="s">
+        <v>320</v>
+      </c>
+      <c r="H71" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <v>67</v>
+      </c>
+      <c r="C72" t="s">
+        <v>322</v>
+      </c>
+      <c r="D72" t="s">
+        <v>323</v>
+      </c>
+      <c r="E72" t="s">
+        <v>323</v>
+      </c>
+      <c r="F72" t="s">
+        <v>324</v>
+      </c>
+      <c r="G72" t="s">
+        <v>325</v>
+      </c>
+      <c r="H72" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73">
+        <v>68</v>
+      </c>
+      <c r="C73" t="s">
+        <v>327</v>
+      </c>
+      <c r="D73" t="s">
+        <v>328</v>
+      </c>
+      <c r="E73" t="s">
+        <v>328</v>
+      </c>
+      <c r="F73" t="s">
+        <v>329</v>
+      </c>
+      <c r="G73" t="s">
+        <v>330</v>
+      </c>
+      <c r="H73" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74">
+        <v>69</v>
+      </c>
+      <c r="C74" t="s">
+        <v>332</v>
+      </c>
+      <c r="D74" t="s">
+        <v>333</v>
+      </c>
+      <c r="E74" t="s">
+        <v>333</v>
+      </c>
+      <c r="F74" t="s">
+        <v>334</v>
+      </c>
+      <c r="G74" t="s">
+        <v>335</v>
+      </c>
+      <c r="H74" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <v>70</v>
+      </c>
+      <c r="C75" t="s">
+        <v>337</v>
+      </c>
+      <c r="D75" t="s">
+        <v>338</v>
+      </c>
+      <c r="E75" t="s">
+        <v>338</v>
+      </c>
+      <c r="F75" t="s">
+        <v>339</v>
+      </c>
+      <c r="G75" t="s">
+        <v>340</v>
+      </c>
+      <c r="H75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B76">
+        <v>71</v>
+      </c>
+      <c r="C76" t="s">
+        <v>341</v>
+      </c>
+      <c r="D76" t="s">
+        <v>342</v>
+      </c>
+      <c r="E76" t="s">
+        <v>342</v>
+      </c>
+      <c r="F76" t="s">
+        <v>343</v>
+      </c>
+      <c r="G76" t="s">
+        <v>344</v>
+      </c>
+      <c r="H76" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
+        <v>346</v>
+      </c>
+      <c r="D77" t="s">
+        <v>347</v>
+      </c>
+      <c r="E77" t="s">
+        <v>347</v>
+      </c>
+      <c r="F77" t="s">
+        <v>348</v>
+      </c>
+      <c r="G77" t="s">
+        <v>349</v>
+      </c>
+      <c r="H77" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <v>73</v>
+      </c>
+      <c r="C78" t="s">
+        <v>351</v>
+      </c>
+      <c r="D78" t="s">
+        <v>352</v>
+      </c>
+      <c r="E78" t="s">
+        <v>352</v>
+      </c>
+      <c r="F78" t="s">
+        <v>353</v>
+      </c>
+      <c r="G78" t="s">
+        <v>354</v>
+      </c>
+      <c r="H78" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B79">
+        <v>74</v>
+      </c>
+      <c r="C79" t="s">
+        <v>356</v>
+      </c>
+      <c r="D79" t="s">
+        <v>357</v>
+      </c>
+      <c r="E79" t="s">
+        <v>357</v>
+      </c>
+      <c r="F79" t="s">
+        <v>345</v>
+      </c>
+      <c r="G79" t="s">
+        <v>344</v>
+      </c>
+      <c r="H79" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B80">
+        <v>75</v>
+      </c>
+      <c r="C80" t="s">
+        <v>359</v>
+      </c>
+      <c r="D80" t="s">
+        <v>360</v>
+      </c>
+      <c r="E80" t="s">
+        <v>360</v>
+      </c>
+      <c r="F80" t="s">
+        <v>361</v>
+      </c>
+      <c r="G80" t="s">
+        <v>362</v>
+      </c>
+      <c r="H80" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <v>76</v>
+      </c>
+      <c r="C81" t="s">
+        <v>364</v>
+      </c>
+      <c r="D81" t="s">
+        <v>365</v>
+      </c>
+      <c r="E81" t="s">
+        <v>365</v>
+      </c>
+      <c r="F81" t="s">
+        <v>366</v>
+      </c>
+      <c r="G81" t="s">
+        <v>367</v>
+      </c>
+      <c r="H81" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B82">
+        <v>77</v>
+      </c>
+      <c r="C82" t="s">
+        <v>369</v>
+      </c>
+      <c r="D82" t="s">
+        <v>370</v>
+      </c>
+      <c r="E82" t="s">
+        <v>370</v>
+      </c>
+      <c r="F82" t="s">
+        <v>371</v>
+      </c>
+      <c r="G82" t="s">
+        <v>372</v>
+      </c>
+      <c r="H82" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B83">
+        <v>78</v>
+      </c>
+      <c r="C83" t="s">
+        <v>374</v>
+      </c>
+      <c r="D83" t="s">
+        <v>375</v>
+      </c>
+      <c r="E83" t="s">
+        <v>375</v>
+      </c>
+      <c r="F83" t="s">
+        <v>376</v>
+      </c>
+      <c r="G83" t="s">
+        <v>377</v>
+      </c>
+      <c r="H83" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <v>79</v>
+      </c>
+      <c r="C84" t="s">
+        <v>378</v>
+      </c>
+      <c r="D84" t="s">
+        <v>379</v>
+      </c>
+      <c r="E84" t="s">
+        <v>379</v>
+      </c>
+      <c r="F84" t="s">
+        <v>380</v>
+      </c>
+      <c r="G84" t="s">
+        <v>381</v>
+      </c>
+      <c r="H84" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B85">
+        <v>80</v>
+      </c>
+      <c r="C85" t="s">
+        <v>383</v>
+      </c>
+      <c r="D85" t="s">
+        <v>384</v>
+      </c>
+      <c r="E85" t="s">
+        <v>384</v>
+      </c>
+      <c r="F85" t="s">
+        <v>385</v>
+      </c>
+      <c r="G85" t="s">
+        <v>386</v>
+      </c>
+      <c r="H85" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
+        <v>387</v>
+      </c>
+      <c r="D86" t="s">
+        <v>388</v>
+      </c>
+      <c r="E86" t="s">
+        <v>388</v>
+      </c>
+      <c r="F86" t="s">
+        <v>389</v>
+      </c>
+      <c r="G86" t="s">
+        <v>390</v>
+      </c>
+      <c r="H86" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>82</v>
+      </c>
+      <c r="C87" t="s">
+        <v>392</v>
+      </c>
+      <c r="D87" t="s">
+        <v>377</v>
+      </c>
+      <c r="E87" t="s">
+        <v>377</v>
+      </c>
+      <c r="F87" t="s">
+        <v>393</v>
+      </c>
+      <c r="G87" t="s">
+        <v>394</v>
+      </c>
+      <c r="H87" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>83</v>
+      </c>
+      <c r="C88" t="s">
+        <v>395</v>
+      </c>
+      <c r="D88" t="s">
+        <v>396</v>
+      </c>
+      <c r="E88" t="s">
+        <v>396</v>
+      </c>
+      <c r="F88" t="s">
+        <v>397</v>
+      </c>
+      <c r="G88" t="s">
+        <v>398</v>
+      </c>
+      <c r="H88" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>84</v>
+      </c>
+      <c r="C89" t="s">
+        <v>400</v>
+      </c>
+      <c r="D89" t="s">
+        <v>401</v>
+      </c>
+      <c r="E89" t="s">
+        <v>401</v>
+      </c>
+      <c r="F89" t="s">
+        <v>402</v>
+      </c>
+      <c r="G89" t="s">
+        <v>377</v>
+      </c>
+      <c r="H89" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>85</v>
+      </c>
+      <c r="C90" t="s">
+        <v>403</v>
+      </c>
+      <c r="D90" t="s">
+        <v>404</v>
+      </c>
+      <c r="E90" t="s">
+        <v>404</v>
+      </c>
+      <c r="F90" t="s">
+        <v>405</v>
+      </c>
+      <c r="G90" t="s">
+        <v>406</v>
+      </c>
+      <c r="H90" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>86</v>
+      </c>
+      <c r="C91" t="s">
+        <v>407</v>
+      </c>
+      <c r="D91" t="s">
+        <v>408</v>
+      </c>
+      <c r="E91" t="s">
+        <v>408</v>
+      </c>
+      <c r="F91" t="s">
+        <v>409</v>
+      </c>
+      <c r="G91" t="s">
+        <v>410</v>
+      </c>
+      <c r="H91" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>87</v>
+      </c>
+      <c r="C92" t="s">
+        <v>412</v>
+      </c>
+      <c r="D92" t="s">
+        <v>413</v>
+      </c>
+      <c r="E92" t="s">
+        <v>413</v>
+      </c>
+      <c r="F92" t="s">
+        <v>414</v>
+      </c>
+      <c r="G92" t="s">
+        <v>415</v>
+      </c>
+      <c r="H92" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>88</v>
+      </c>
+      <c r="C93" t="s">
+        <v>417</v>
+      </c>
+      <c r="D93" t="s">
+        <v>418</v>
+      </c>
+      <c r="E93" t="s">
+        <v>418</v>
+      </c>
+      <c r="F93" t="s">
+        <v>419</v>
+      </c>
+      <c r="G93" t="s">
+        <v>420</v>
+      </c>
+      <c r="H93" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>89</v>
+      </c>
+      <c r="C94" t="s">
+        <v>422</v>
+      </c>
+      <c r="D94" t="s">
+        <v>423</v>
+      </c>
+      <c r="E94" t="s">
+        <v>423</v>
+      </c>
+      <c r="F94" t="s">
+        <v>424</v>
+      </c>
+      <c r="G94" t="s">
+        <v>421</v>
+      </c>
+      <c r="H94" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>90</v>
+      </c>
+      <c r="C95" t="s">
+        <v>426</v>
+      </c>
+      <c r="D95" t="s">
+        <v>427</v>
+      </c>
+      <c r="E95" t="s">
+        <v>427</v>
+      </c>
+      <c r="F95" t="s">
+        <v>428</v>
+      </c>
+      <c r="G95" t="s">
+        <v>429</v>
+      </c>
+      <c r="H95" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>91</v>
+      </c>
+      <c r="C96" t="s">
+        <v>431</v>
+      </c>
+      <c r="D96" t="s">
+        <v>360</v>
+      </c>
+      <c r="E96" t="s">
+        <v>360</v>
+      </c>
+      <c r="F96" t="s">
+        <v>361</v>
+      </c>
+      <c r="G96" t="s">
+        <v>210</v>
+      </c>
+      <c r="H96" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>92</v>
+      </c>
+      <c r="C97" t="s">
+        <v>433</v>
+      </c>
+      <c r="D97" t="s">
+        <v>434</v>
+      </c>
+      <c r="E97" t="s">
+        <v>434</v>
+      </c>
+      <c r="F97" t="s">
+        <v>435</v>
+      </c>
+      <c r="G97" t="s">
+        <v>436</v>
+      </c>
+      <c r="H97" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>93</v>
+      </c>
+      <c r="C98" t="s">
+        <v>438</v>
+      </c>
+      <c r="D98" t="s">
+        <v>439</v>
+      </c>
+      <c r="E98" t="s">
+        <v>439</v>
+      </c>
+      <c r="F98" t="s">
+        <v>440</v>
+      </c>
+      <c r="G98" t="s">
+        <v>441</v>
+      </c>
+      <c r="H98" t="s">
+        <v>406</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
